--- a/tabular/refseq-core/ifnl-refseq-side-data.xlsx
+++ b/tabular/refseq-core/ifnl-refseq-side-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/host/IFNL-Evolution/tabular/refseq-core/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D682C36-485E-104B-843A-E18262D77B5E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003423D1-9323-AD4C-920F-B4B1D1427B42}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="500" windowWidth="27860" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="960" yWindow="500" windowWidth="27840" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="A+B" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="133">
   <si>
     <t>NM_001346937.1</t>
   </si>
@@ -427,6 +427,12 @@
   </si>
   <si>
     <t>REF_IFNL_Archelosauria_1_Crocodylia</t>
+  </si>
+  <si>
+    <t>mammalian_b_n_terminus</t>
+  </si>
+  <si>
+    <t>Placental2</t>
   </si>
 </sst>
 </file>
@@ -2036,7 +2042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -2052,9 +2058,10 @@
     <col min="11" max="11" width="21.33203125" customWidth="1"/>
     <col min="12" max="12" width="15.83203125" style="12" customWidth="1"/>
     <col min="13" max="13" width="10.83203125" style="12"/>
+    <col min="14" max="14" width="26.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -2094,8 +2101,11 @@
       <c r="M1" s="11" t="s">
         <v>52</v>
       </c>
+      <c r="N1" s="11" t="s">
+        <v>131</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="22" t="s">
         <v>23</v>
       </c>
@@ -2131,8 +2141,9 @@
       </c>
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
         <v>28</v>
       </c>
@@ -2168,8 +2179,9 @@
       </c>
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="22" t="s">
         <v>104</v>
       </c>
@@ -2205,8 +2217,9 @@
       </c>
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="22" t="s">
         <v>27</v>
       </c>
@@ -2242,8 +2255,9 @@
       </c>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="22" t="s">
         <v>24</v>
       </c>
@@ -2279,8 +2293,9 @@
       </c>
       <c r="L6" s="16"/>
       <c r="M6" s="16"/>
+      <c r="N6" s="17"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
         <v>59</v>
       </c>
@@ -2316,8 +2331,9 @@
       </c>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
         <v>21</v>
       </c>
@@ -2357,8 +2373,9 @@
       <c r="M8" s="15" t="s">
         <v>15</v>
       </c>
+      <c r="N8" s="17"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
         <v>20</v>
       </c>
@@ -2398,8 +2415,11 @@
       <c r="M9" s="18" t="s">
         <v>15</v>
       </c>
+      <c r="N9" s="17" t="s">
+        <v>132</v>
+      </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="22" t="s">
         <v>26</v>
       </c>
@@ -2435,8 +2455,9 @@
       </c>
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="22" t="s">
         <v>25</v>
       </c>
@@ -2472,6 +2493,10 @@
       </c>
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="17"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M11">
